--- a/excel/skills.xlsx
+++ b/excel/skills.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaoyu\OneDrive\桌面\gbfai代码\1228\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C42556F-FB99-4B1C-B57C-0F5061A3E7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F3DBAC-93D0-4AC0-A6E8-D36477277F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13500" yWindow="6015" windowWidth="34485" windowHeight="15690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11295" yWindow="6135" windowWidth="34485" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
   <si>
     <t>名称</t>
   </si>
@@ -120,13 +120,113 @@
   <si>
     <t>属性角色的技能伤害上升（10万）</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimus_impalement_big</t>
+  </si>
+  <si>
+    <t>神石的贯破大</t>
+  </si>
+  <si>
+    <t>属性角色无视敌方防御力（大）
+属性角色的攻击力提升（小）</t>
+  </si>
+  <si>
+    <t>weapon</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>weapon_def_ignore</t>
+  </si>
+  <si>
+    <t>optimus</t>
+  </si>
+  <si>
+    <t>10:1.75% 15:2%</t>
+  </si>
+  <si>
+    <t>weapon_normal_atk</t>
+  </si>
+  <si>
+    <t>10:10% 15:12%</t>
+  </si>
+  <si>
+    <t>optimus_demolishment_big</t>
+  </si>
+  <si>
+    <t>神石的冲破大</t>
+  </si>
+  <si>
+    <t>属性角色的普通攻击伤害增幅提升（大）</t>
+  </si>
+  <si>
+    <t>weapon_na_dmg_amp</t>
+  </si>
+  <si>
+    <t>10:2.5% 15:3%</t>
+  </si>
+  <si>
+    <t>optimus_stratagem_big</t>
+  </si>
+  <si>
+    <t>神石的战技大</t>
+  </si>
+  <si>
+    <t>属性角色暴击时，伤害增幅（大）</t>
+  </si>
+  <si>
+    <t>weapon_critical_hit_amp</t>
+  </si>
+  <si>
+    <t>10:1.4% 15:1.8%</t>
+  </si>
+  <si>
+    <t>element_maneuver</t>
+  </si>
+  <si>
+    <t>属性的武技</t>
+  </si>
+  <si>
+    <t>属性角色的普通攻击伤害上升（上限5万）</t>
+  </si>
+  <si>
+    <t>weapon_na_dmg_supp</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>optimus_onslaught_big</t>
+  </si>
+  <si>
+    <t>神石的袭奥大</t>
+  </si>
+  <si>
+    <t>属性角色发动奥义时，额外造成1次属性伤害（大）</t>
+  </si>
+  <si>
+    <t>weapon_elem_bonus_ca</t>
+  </si>
+  <si>
+    <t>optimus_rigor_big</t>
+  </si>
+  <si>
+    <t>神石的冴手大</t>
+  </si>
+  <si>
+    <t>属性角色造成技能伤害时，额外造成1次属性伤害（大）</t>
+  </si>
+  <si>
+    <t>weapon_elem_bonus_skill</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +250,22 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -205,7 +321,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -216,6 +332,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -485,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
@@ -595,6 +723,222 @@
       <c r="K2">
         <v>100000</v>
       </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="5">
+        <v>50000</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/excel/skills.xlsx
+++ b/excel/skills.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaoyu\OneDrive\桌面\gbfai代码\1228\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F3DBAC-93D0-4AC0-A6E8-D36477277F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348B2645-89B1-4015-989B-E32839135FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11295" yWindow="6135" windowWidth="34485" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7305" yWindow="4905" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
   <si>
     <t>名称</t>
   </si>
@@ -220,13 +220,113 @@
   </si>
   <si>
     <t>weapon_elem_bonus_skill</t>
+  </si>
+  <si>
+    <t>guiding_star_splendor</t>
+  </si>
+  <si>
+    <t>极星的光辉</t>
+  </si>
+  <si>
+    <t>攻击力+30%、HP +30%、防御力 +25%</t>
+  </si>
+  <si>
+    <t>weapon_def</t>
+  </si>
+  <si>
+    <t>weapon_hp</t>
+  </si>
+  <si>
+    <t>destruction_godblade3</t>
+  </si>
+  <si>
+    <t>破坏的神刃3</t>
+  </si>
+  <si>
+    <t>属性角色的攻击力提升（特大） 
+属性角色获得破坏属性追击（特大）</t>
+  </si>
+  <si>
+    <t>weapon_ex_atk</t>
+  </si>
+  <si>
+    <t>weapon_des_bonus_na</t>
+  </si>
+  <si>
+    <t>rebirth_godshield3</t>
+  </si>
+  <si>
+    <t>再生的神守3</t>
+  </si>
+  <si>
+    <t>属性角色的HP最大值提升（特大） 
+属性角色发动奥义时，额外造成1次破坏属性伤害（特大）</t>
+  </si>
+  <si>
+    <t>weapon_des_bonus_ca</t>
+  </si>
+  <si>
+    <t>optimus_might_big</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>神石的攻刃大</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性角色的攻击力提升（大）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>weapon_normal_atk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimus</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>odious_fandango_medium</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>禁呪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>乱舞中</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【禁祸】属性角色攻击力提升（中）
+属性角色的TA几率提升（中）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +370,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -321,7 +428,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -345,6 +452,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -613,11 +735,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" customWidth="1"/>
     <col min="3" max="3" width="31.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
@@ -940,10 +1062,194 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="11" spans="1:23" ht="36" x14ac:dyDescent="0.15">
+      <c r="A11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
